--- a/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>DFS</t>
   </si>
@@ -656,215 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4868000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4610000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4290000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4077000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3856000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3357000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2915000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2736000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2742000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2674000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2589000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2646000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2760000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2681000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2672000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2982000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3039000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3040000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2977000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2937000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2907000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2781000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2636000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2569000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2556000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2476000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2338000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2278000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2258000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2184000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -955,8 +961,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1047,8 +1056,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1081,8 +1093,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1186,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1265,8 +1281,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1357,8 +1376,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1449,8 +1471,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1480,192 +1505,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3309000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2990000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2418000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2047000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1672000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1287000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>854000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>411000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>522000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>454000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>425000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-49000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>383000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>416000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>482000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>584000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1451000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1437000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1432000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1441000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1405000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1300000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1249000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1220000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1115000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1100000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1040000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>972000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>944000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1620000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1872000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2030000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2184000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2070000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2061000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2325000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>2220000</v>
       </c>
       <c r="L18" s="3">
         <v>2220000</v>
       </c>
       <c r="M18" s="3">
+        <v>2220000</v>
+      </c>
+      <c r="N18" s="3">
         <v>2164000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2695000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2377000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2265000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2190000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2398000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1588000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1603000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1545000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1496000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1502000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1481000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1387000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1349000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1441000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1376000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1298000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1306000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1314000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1380000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1698,192 +1730,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1047000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-732000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-703000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-773000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-830000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-841000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-743000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-620000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-707000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-859000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-818000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>58000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-616000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1362000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1306000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2651000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2476000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-664000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-609000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-558000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-566000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-605000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-514000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-510000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-493000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-542000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-473000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-438000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-419000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>616000</v>
+      </c>
+      <c r="E21" s="3">
         <v>994000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1288000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1386000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1491000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1480000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1472000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1581000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1757000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1505000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1541000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2351000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2198000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1138000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1075000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-338000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>45000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1045000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1107000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1090000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1029000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1006000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1077000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>986000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>963000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1004000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>962000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>961000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>972000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1974,192 +2013,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>512000</v>
+      </c>
+      <c r="E23" s="3">
         <v>888000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1169000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1257000</v>
       </c>
-      <c r="G23" s="3">
-        <v>1354000</v>
-      </c>
       <c r="H23" s="3">
+        <v>1343000</v>
+      </c>
+      <c r="I23" s="3">
         <v>1327000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1441000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1618000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1361000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1402000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2222000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2079000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1015000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>959000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-461000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-78000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>924000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>994000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>987000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>930000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>897000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>967000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>877000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>856000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>899000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>903000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>867000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>868000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>883000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>961000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E24" s="3">
         <v>205000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>268000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>289000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>318000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>314000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>338000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>376000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>294000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>311000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>524000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>486000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>216000</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>188000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>216000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>224000</v>
+      </c>
+      <c r="V24" s="3">
+        <v>234000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>204000</v>
+      </c>
+      <c r="X24" s="3">
+        <v>210000</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>247000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>208000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>190000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>323000</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>301000</v>
+      </c>
+      <c r="AD24" s="3">
         <v>321000</v>
       </c>
-      <c r="H24" s="3">
-        <v>314000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>338000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>376000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>294000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>311000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>524000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>486000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>216000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>188000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-93000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>216000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>224000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>234000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>204000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>210000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>247000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>208000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>190000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>323000</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>301000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>321000</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>304000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>320000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>322000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2250,192 +2298,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>388000</v>
+      </c>
+      <c r="E26" s="3">
         <v>683000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>901000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>968000</v>
       </c>
-      <c r="G26" s="3">
-        <v>1033000</v>
-      </c>
       <c r="H26" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="I26" s="3">
         <v>1013000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1103000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1242000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1067000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1091000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1698000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1593000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>799000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>771000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-368000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-61000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>708000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>770000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>753000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>726000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>687000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>720000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>669000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>666000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>576000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>602000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>546000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>564000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>563000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E27" s="3">
         <v>647000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>895000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>931000</v>
       </c>
-      <c r="G27" s="3">
-        <v>1027000</v>
-      </c>
       <c r="H27" s="3">
+        <v>1019000</v>
+      </c>
+      <c r="I27" s="3">
         <v>975000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1097000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1205000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1062000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1055000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1688000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1546000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>795000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>751000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-369000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-78000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>705000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>749000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>747000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>705000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>681000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>699000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>663000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>646000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>548000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>589000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>532000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>551000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>550000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2526,8 +2583,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2582,8 +2642,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2600,12 +2660,12 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-189000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2618,8 +2678,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2710,8 +2773,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2802,192 +2868,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1047000</v>
+      </c>
+      <c r="E32" s="3">
         <v>732000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>703000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>773000</v>
       </c>
-      <c r="G32" s="3">
-        <v>830000</v>
-      </c>
       <c r="H32" s="3">
+        <v>841000</v>
+      </c>
+      <c r="I32" s="3">
         <v>743000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>620000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>707000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>859000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>818000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-58000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>616000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1362000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1306000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2651000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2476000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>664000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>609000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>558000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>566000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>605000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>514000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>510000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>493000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>542000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>473000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>431000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>438000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>431000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>419000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E33" s="3">
         <v>647000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>895000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>931000</v>
       </c>
-      <c r="G33" s="3">
-        <v>1027000</v>
-      </c>
       <c r="H33" s="3">
+        <v>1019000</v>
+      </c>
+      <c r="I33" s="3">
         <v>975000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1097000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1205000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1062000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1055000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1688000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1546000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>795000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>751000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-369000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-78000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>705000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>749000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>747000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>705000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>681000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>699000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>663000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>646000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>359000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>589000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>532000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>551000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>550000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3078,197 +3153,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E35" s="3">
         <v>647000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>895000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>931000</v>
       </c>
-      <c r="G35" s="3">
-        <v>1027000</v>
-      </c>
       <c r="H35" s="3">
+        <v>1019000</v>
+      </c>
+      <c r="I35" s="3">
         <v>975000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1097000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1205000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1062000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1055000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1688000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1546000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>795000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>751000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-369000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-78000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>705000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>749000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>747000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>705000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>681000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>699000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>663000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>646000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>359000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>589000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>532000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>551000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>550000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3301,8 +3385,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3335,100 +3420,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11685000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9194000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8605000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10130000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8856000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10004000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11439000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9625000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8750000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12716000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15445000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20348000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13564000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9513000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15138000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10028000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6924000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6075000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10313000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15169000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13299000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16019000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>15289000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>17011000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13306000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13249000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12950000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15163000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11914000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12076000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3466,22 +3555,22 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>2200000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8048000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2549000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T42" s="3">
-        <v>1000000</v>
+      <c r="T42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U42" s="3">
         <v>1000000</v>
@@ -3489,8 +3578,8 @@
       <c r="V42" s="3">
         <v>1000000</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>5</v>
+      <c r="W42" s="3">
+        <v>1000000</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>5</v>
@@ -3501,8 +3590,8 @@
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3510,17 +3599,20 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
+      <c r="AD42" s="3">
+        <v>0</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="3">
         <v>850000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3611,8 +3703,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3703,8 +3798,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3795,8 +3893,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3887,192 +3988,201 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>514000</v>
+      </c>
+      <c r="E47" s="3">
         <v>426000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>411000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>406000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>416000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>382000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>366000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>377000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>388000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>366000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>343000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>342000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>353000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>323000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>335000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>348000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>336000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>321000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>310000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>284000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>295000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>263000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>275000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>286000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>297000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>349000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>332000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>319000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>326000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>298000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1091000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1084000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1053000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1031000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1003000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1015000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>984000</v>
       </c>
       <c r="J48" s="3">
         <v>984000</v>
       </c>
       <c r="K48" s="3">
+        <v>984000</v>
+      </c>
+      <c r="L48" s="3">
         <v>983000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>987000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>986000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1021000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1027000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1121000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1115000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1070000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1106000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1028000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1008000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>980000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>936000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>896000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>874000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>848000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>825000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>800000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>774000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>750000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>734000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>722000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4101,13 +4211,13 @@
         <v>255000</v>
       </c>
       <c r="L49" s="3">
-        <v>256000</v>
+        <v>255000</v>
       </c>
       <c r="M49" s="3">
         <v>256000</v>
       </c>
       <c r="N49" s="3">
-        <v>350000</v>
+        <v>256000</v>
       </c>
       <c r="O49" s="3">
         <v>350000</v>
@@ -4116,28 +4226,28 @@
         <v>350000</v>
       </c>
       <c r="Q49" s="3">
+        <v>350000</v>
+      </c>
+      <c r="R49" s="3">
         <v>351000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>410000</v>
       </c>
       <c r="S49" s="3">
         <v>410000</v>
       </c>
       <c r="T49" s="3">
+        <v>410000</v>
+      </c>
+      <c r="U49" s="3">
         <v>414000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>415000</v>
       </c>
       <c r="V49" s="3">
         <v>415000</v>
       </c>
       <c r="W49" s="3">
+        <v>415000</v>
+      </c>
+      <c r="X49" s="3">
         <v>416000</v>
-      </c>
-      <c r="X49" s="3">
-        <v>417000</v>
       </c>
       <c r="Y49" s="3">
         <v>417000</v>
@@ -4146,25 +4256,28 @@
         <v>417000</v>
       </c>
       <c r="AA49" s="3">
-        <v>418000</v>
+        <v>417000</v>
       </c>
       <c r="AB49" s="3">
         <v>418000</v>
       </c>
       <c r="AC49" s="3">
+        <v>418000</v>
+      </c>
+      <c r="AD49" s="3">
         <v>419000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>420000</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>421000</v>
       </c>
       <c r="AF49" s="3">
         <v>421000</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>421000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4255,8 +4368,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4347,8 +4463,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4439,8 +4558,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4531,100 +4653,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>151522000</v>
+      </c>
+      <c r="E54" s="3">
         <v>143432000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>138082000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>133061000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>131706000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>121886000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>114600000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>107412000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>110242000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>108544000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>110985000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>113871000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>112889000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>124349000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>113792000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>112657000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>113996000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>110786000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>110707000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>110720000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>109553000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>105842000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>102751000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>101967000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>100087000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>97608000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>93757000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>94795000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>92308000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>90541000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4657,8 +4785,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4691,8 +4820,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4783,192 +4913,201 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>532000</v>
+        <v>4476000</v>
       </c>
       <c r="E58" s="3">
-        <v>1837000</v>
+        <v>7000</v>
       </c>
       <c r="F58" s="3">
-        <v>1841000</v>
+        <v>1312000</v>
       </c>
       <c r="G58" s="3">
-        <v>3815000</v>
+        <v>1316000</v>
       </c>
       <c r="H58" s="3">
+        <v>3290000</v>
+      </c>
+      <c r="I58" s="3">
         <v>2331000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4122000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2638000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6935000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>5126000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4195000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4217000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11250000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1854000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4759000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5247000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>200000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2475000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3672000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6511000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1549000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2773000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3270000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5272000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1201000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2201000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4250000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5100000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1250000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6432000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5710000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4963000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4843000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5618000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4526000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4439000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4365000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4214000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4203000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3988000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3961000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3860000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3541000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3591000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3476000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3690000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3594000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4317000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4269000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3436000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4154000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3927000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3722000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4105000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3549000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3196000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3185000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3550000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3119000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5059,100 +5198,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18935000</v>
+        <v>15807000</v>
       </c>
       <c r="E61" s="3">
+        <v>18412000</v>
+      </c>
+      <c r="F61" s="3">
         <v>18439000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16322000</v>
       </c>
-      <c r="G61" s="3">
-        <v>20108000</v>
-      </c>
       <c r="H61" s="3">
+        <v>19583000</v>
+      </c>
+      <c r="I61" s="3">
         <v>17846000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15863000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14494000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13292000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18516000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14224000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16816000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>17024000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21291000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21340000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21339000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>20454000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24254000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>22688000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>22604000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20717000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>25449000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>23479000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>22974000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>21054000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>25536000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>24237000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>22573000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20343000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>25580000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5243,8 +5388,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5335,8 +5483,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5427,8 +5578,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5519,100 +5673,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>136694000</v>
+      </c>
+      <c r="E66" s="3">
         <v>129196000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>124226000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>118746000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>117362000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>107600000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>100836000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>93979000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>96834000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>95281000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>97814000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>101717000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>102005000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>114097000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>104149000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>102992000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>102137000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>99069000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>99214000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>99461000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>98423000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>94826000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>91862000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>91096000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>89195000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>86421000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>82498000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>83530000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>80985000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>79194000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5645,8 +5805,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5737,8 +5898,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5829,8 +5993,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5877,7 +6044,7 @@
         <v>1056000</v>
       </c>
       <c r="R70" s="3">
-        <v>563000</v>
+        <v>1056000</v>
       </c>
       <c r="S70" s="3">
         <v>563000</v>
@@ -5907,7 +6074,7 @@
         <v>563000</v>
       </c>
       <c r="AB70" s="3">
-        <v>560000</v>
+        <v>563000</v>
       </c>
       <c r="AC70" s="3">
         <v>560000</v>
@@ -5921,8 +6088,11 @@
       <c r="AF70" s="3">
         <v>560000</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6013,100 +6183,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>30448000</v>
+      </c>
+      <c r="E72" s="3">
         <v>30236000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29761000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29292000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28207000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27585000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26776000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25833000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>24766000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23846000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22936000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21373000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19955000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19292000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18673000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19175000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>21290000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20720000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>20107000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19484000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18906000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18354000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17787000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17211000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>16687000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>16452000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15989000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15568000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15130000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14696000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6197,8 +6373,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6289,8 +6468,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6381,100 +6563,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13772000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13180000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12800000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13259000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13288000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13230000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12708000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12377000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12352000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12207000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12115000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11098000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9828000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9196000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8587000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9102000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11296000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11154000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10930000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10696000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10567000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10453000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10326000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10308000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10329000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10627000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10699000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10705000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10763000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10787000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6565,197 +6753,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E81" s="3">
         <v>647000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>895000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>931000</v>
       </c>
-      <c r="G81" s="3">
-        <v>1027000</v>
-      </c>
       <c r="H81" s="3">
+        <v>1019000</v>
+      </c>
+      <c r="I81" s="3">
         <v>975000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1097000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1205000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1062000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1055000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1688000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1546000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>795000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>751000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-369000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-78000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>705000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>749000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>747000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>705000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>681000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>699000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>663000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>646000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>359000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>589000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>532000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>551000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>550000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6788,100 +6985,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E83" s="3">
         <v>106000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>119000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>129000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>137000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>145000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>140000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>139000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>144000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>139000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>129000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>119000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>123000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>116000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>123000</v>
       </c>
       <c r="R83" s="3">
         <v>123000</v>
       </c>
       <c r="S83" s="3">
+        <v>123000</v>
+      </c>
+      <c r="T83" s="3">
         <v>121000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>113000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>103000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>99000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>109000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>110000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>109000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>107000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>104000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>101000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>95000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>93000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>89000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6972,8 +7173,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7064,8 +7268,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7156,8 +7363,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7248,8 +7458,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7340,100 +7553,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2876000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2389000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1507000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1791000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2175000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1619000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1612000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1734000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1342000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1621000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1548000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1508000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1633000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1296000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1587000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1680000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1464000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>819000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1578000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2335000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>761000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1606000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1586000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1238000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1624000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1552000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1019000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1013000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1292000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1317000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7466,100 +7685,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-77000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-82000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-76000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-79000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-48000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-51000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-48000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-49000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-56000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-55000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-94000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-59000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-72000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-61000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-69000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-82000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-77000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-59000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-57000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-56000</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-47000</v>
       </c>
       <c r="AE91" s="3">
         <v>-47000</v>
       </c>
       <c r="AF91" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-46000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7650,8 +7873,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7742,100 +7968,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6822000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5836000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7604000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1229000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13014000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7490000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5794000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>661000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3391000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1510000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1247000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>6188000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3696000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5575000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>996000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2397000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3055000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6030000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4421000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1768000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5814000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3036000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2645000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>916000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4273000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2919000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1568000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2291000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2007000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7868,100 +8100,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-176000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-177000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-192000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-144000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-165000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-166000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-183000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-129000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-147000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-151000</v>
       </c>
       <c r="M96" s="3">
         <v>-151000</v>
       </c>
       <c r="N96" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-120000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-152000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-151000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-122000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-153000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-126000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-145000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-118000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-151000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-122000</v>
       </c>
       <c r="Y96" s="3">
         <v>-122000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-142000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-137000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-124000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-127000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-128000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-132000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8052,8 +8288,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8144,8 +8383,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8236,100 +8478,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6441000</v>
+      </c>
+      <c r="E100" s="3">
         <v>4036000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4578000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>704000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7866000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6270000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6010000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4084000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>633000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3731000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4607000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-611000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1829000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-799000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1373000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>170000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2443000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-30000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1017000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-499000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3589000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2120000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-120000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1557000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1522000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2850000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1664000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2253000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>837000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2149000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8420,96 +8668,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2495000</v>
+      </c>
+      <c r="E102" s="3">
         <v>589000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1519000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1266000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2973000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>399000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1828000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1689000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1416000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3620000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4306000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7085000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3500000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5078000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3956000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4247000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>852000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5241000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3860000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>68000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1464000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>690000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1179000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3711000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1483000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2213000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3249000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-162000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1459000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>DFS</t>
   </si>
@@ -656,221 +656,227 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4948000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4868000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4610000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4290000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4077000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3856000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3357000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2915000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2736000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2742000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2674000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2589000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2646000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2760000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2681000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2672000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2982000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3039000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3040000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2977000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2937000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2907000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2781000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2636000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2569000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2556000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2476000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2338000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2278000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2258000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2184000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -964,8 +970,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,8 +1068,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1094,8 +1106,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1189,8 +1202,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1284,8 +1300,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1379,8 +1398,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1474,8 +1496,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1506,198 +1531,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2958000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3309000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2990000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2418000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2047000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1672000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1287000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>854000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>411000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>522000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>454000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>425000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-49000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>383000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>416000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>482000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>584000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1451000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1437000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1432000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1441000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1405000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1300000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1249000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1220000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1115000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1100000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1040000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>972000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>944000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1990000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1559000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1620000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1872000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2030000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2184000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2070000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2061000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2325000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>2220000</v>
       </c>
       <c r="M18" s="3">
         <v>2220000</v>
       </c>
       <c r="N18" s="3">
+        <v>2220000</v>
+      </c>
+      <c r="O18" s="3">
         <v>2164000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2695000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2377000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2265000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2190000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2398000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1588000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1603000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1545000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1496000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1502000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1481000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1387000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1349000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1441000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1376000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1298000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1306000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1314000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1380000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1731,198 +1763,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1586000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1047000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-732000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-703000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-773000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-841000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-743000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-620000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-707000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-859000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-818000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>58000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-616000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1362000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1306000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2651000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2476000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-664000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-609000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-558000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-566000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-605000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-514000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-510000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-493000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-542000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-473000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-438000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-419000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E21" s="3">
         <v>616000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>994000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1288000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1386000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1480000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1472000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1581000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1757000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1505000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1541000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2351000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2198000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1138000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1075000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-338000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>45000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1045000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1107000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1090000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1029000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1006000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1077000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>986000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>963000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1004000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>962000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>961000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>972000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2016,198 +2055,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>404000</v>
+      </c>
+      <c r="E23" s="3">
         <v>512000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>888000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1169000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1257000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1343000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1327000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1441000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1618000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1361000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1402000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2222000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2079000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1015000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>959000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-461000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-78000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>924000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>994000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>987000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>930000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>897000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>967000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>877000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>856000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>899000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>903000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>867000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>868000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>883000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>961000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E24" s="3">
         <v>124000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>205000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>268000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>289000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>318000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>314000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>338000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>376000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>294000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>311000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>524000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>486000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>216000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>188000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-93000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-17000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>216000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>224000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>234000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>204000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>210000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>247000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>208000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>190000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>323000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>301000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>321000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>304000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>320000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>322000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2301,198 +2349,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E26" s="3">
         <v>388000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>683000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>901000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>968000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1025000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1013000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1103000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1242000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1067000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1091000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1698000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1593000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>799000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>771000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-368000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-61000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>708000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>770000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>753000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>726000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>687000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>720000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>669000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>666000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>576000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>602000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>546000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>564000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>563000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E27" s="3">
         <v>386000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>647000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>895000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>931000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1019000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>975000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1097000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1205000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1062000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1055000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1688000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1546000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>795000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>751000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-369000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-78000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>705000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>749000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>747000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>705000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>681000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>699000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>663000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>646000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>548000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>589000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>532000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>551000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>550000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2586,8 +2643,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2645,8 +2705,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2663,12 +2723,12 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-189000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2681,8 +2741,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2776,8 +2839,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2871,198 +2937,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1586000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1047000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>732000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>703000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>773000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>841000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>743000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>620000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>707000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>859000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>818000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-58000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>616000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1362000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1306000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2651000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2476000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>664000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>609000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>558000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>566000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>605000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>514000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>510000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>493000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>542000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>473000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>431000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>438000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>431000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>419000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E33" s="3">
         <v>386000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>647000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>895000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>931000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1019000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>975000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1097000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1205000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1062000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1055000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1688000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1546000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>795000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>751000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-369000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-78000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>705000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>749000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>747000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>705000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>681000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>699000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>663000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>646000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>359000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>589000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>532000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>551000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>550000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3156,203 +3231,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E35" s="3">
         <v>386000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>647000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>895000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>931000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1019000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>975000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1097000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1205000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1062000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1055000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1688000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1546000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>795000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>751000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-369000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-78000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>705000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>749000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>747000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>705000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>681000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>699000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>663000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>646000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>359000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>589000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>532000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>551000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>550000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3386,8 +3470,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3421,103 +3506,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14004000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11685000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9194000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8605000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10130000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8856000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10004000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11439000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9625000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8750000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12716000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15445000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20348000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13564000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9513000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>15138000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10028000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6924000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6075000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10313000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>15169000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13299000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16019000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15289000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>17011000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13306000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13249000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12950000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>15163000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11914000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>12076000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3558,22 +3647,22 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>2200000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>8048000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2549000</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U42" s="3">
-        <v>1000000</v>
+      <c r="U42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V42" s="3">
         <v>1000000</v>
@@ -3581,8 +3670,8 @@
       <c r="W42" s="3">
         <v>1000000</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>5</v>
+      <c r="X42" s="3">
+        <v>1000000</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>5</v>
@@ -3593,8 +3682,8 @@
       <c r="AA42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3602,17 +3691,20 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
+      <c r="AE42" s="3">
+        <v>0</v>
       </c>
       <c r="AF42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>850000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3706,8 +3798,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3801,8 +3896,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3896,8 +3994,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3991,198 +4092,207 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E47" s="3">
         <v>514000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>426000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>411000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>406000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>416000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>382000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>366000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>377000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>388000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>366000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>343000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>342000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>353000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>323000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>335000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>348000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>336000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>321000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>310000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>284000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>295000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>263000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>275000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>286000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>297000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>349000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>332000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>319000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>326000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>298000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1107000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1091000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1084000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1053000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1031000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1003000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1015000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>984000</v>
       </c>
       <c r="K48" s="3">
         <v>984000</v>
       </c>
       <c r="L48" s="3">
+        <v>984000</v>
+      </c>
+      <c r="M48" s="3">
         <v>983000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>987000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>986000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1021000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1027000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1121000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1115000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1070000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1106000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1028000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1008000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>980000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>936000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>896000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>874000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>848000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>825000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>800000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>774000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>750000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>734000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>722000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4214,13 +4324,13 @@
         <v>255000</v>
       </c>
       <c r="M49" s="3">
-        <v>256000</v>
+        <v>255000</v>
       </c>
       <c r="N49" s="3">
         <v>256000</v>
       </c>
       <c r="O49" s="3">
-        <v>350000</v>
+        <v>256000</v>
       </c>
       <c r="P49" s="3">
         <v>350000</v>
@@ -4229,28 +4339,28 @@
         <v>350000</v>
       </c>
       <c r="R49" s="3">
+        <v>350000</v>
+      </c>
+      <c r="S49" s="3">
         <v>351000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>410000</v>
       </c>
       <c r="T49" s="3">
         <v>410000</v>
       </c>
       <c r="U49" s="3">
+        <v>410000</v>
+      </c>
+      <c r="V49" s="3">
         <v>414000</v>
-      </c>
-      <c r="V49" s="3">
-        <v>415000</v>
       </c>
       <c r="W49" s="3">
         <v>415000</v>
       </c>
       <c r="X49" s="3">
+        <v>415000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>416000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>417000</v>
       </c>
       <c r="Z49" s="3">
         <v>417000</v>
@@ -4259,25 +4369,28 @@
         <v>417000</v>
       </c>
       <c r="AB49" s="3">
-        <v>418000</v>
+        <v>417000</v>
       </c>
       <c r="AC49" s="3">
         <v>418000</v>
       </c>
       <c r="AD49" s="3">
+        <v>418000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>419000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>420000</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>421000</v>
       </c>
       <c r="AG49" s="3">
         <v>421000</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>421000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4371,8 +4484,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4466,8 +4582,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4561,8 +4680,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4656,103 +4778,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>152689000</v>
+      </c>
+      <c r="E54" s="3">
         <v>151522000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>143432000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>138082000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>133061000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>131706000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>121886000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>114600000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>107412000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>110242000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>108544000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>110985000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>113871000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>112889000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>124349000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>113792000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>112657000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>113996000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>110786000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>110707000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>110720000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>109553000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>105842000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>102751000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>101967000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>100087000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>97608000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>93757000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>94795000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>92308000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>90541000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4786,8 +4914,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4821,8 +4950,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4916,198 +5046,207 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3725000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4476000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1312000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1316000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3290000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2331000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4122000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2638000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6935000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>5126000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4195000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4217000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11250000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1854000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4759000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5247000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>200000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2475000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3672000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6511000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1549000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2773000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3270000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5272000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1201000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2201000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4250000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5100000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1250000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7064000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6432000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5710000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4963000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4843000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5618000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4526000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4439000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4365000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4214000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4203000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3988000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3961000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3860000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3541000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3591000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3476000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3690000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3594000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4317000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4269000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3436000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4154000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3927000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3722000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4105000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3549000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3196000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3185000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3550000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3119000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5201,103 +5340,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15702000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15807000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18412000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18439000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16322000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19583000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17846000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15863000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14494000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13292000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18516000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14224000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16816000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>17024000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21291000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21340000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21339000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>20454000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24254000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>22688000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>22604000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>20717000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>25449000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>23479000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>22974000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>21054000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>25536000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>24237000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>22573000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>20343000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>25580000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5391,8 +5536,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5486,8 +5634,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5581,8 +5732,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5676,103 +5830,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>137969000</v>
+      </c>
+      <c r="E66" s="3">
         <v>136694000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>129196000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>124226000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>118746000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>117362000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>107600000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100836000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>93979000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>96834000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>95281000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>97814000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>101717000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>102005000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>114097000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>104149000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>102992000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>102137000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>99069000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>99214000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>99461000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>98423000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>94826000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>91862000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>91096000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>89195000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>86421000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>82498000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>83530000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>80985000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>79194000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5806,8 +5966,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5901,8 +6062,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5996,8 +6160,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6047,7 +6214,7 @@
         <v>1056000</v>
       </c>
       <c r="S70" s="3">
-        <v>563000</v>
+        <v>1056000</v>
       </c>
       <c r="T70" s="3">
         <v>563000</v>
@@ -6077,7 +6244,7 @@
         <v>563000</v>
       </c>
       <c r="AC70" s="3">
-        <v>560000</v>
+        <v>563000</v>
       </c>
       <c r="AD70" s="3">
         <v>560000</v>
@@ -6091,8 +6258,11 @@
       <c r="AG70" s="3">
         <v>560000</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6186,103 +6356,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>30511000</v>
+      </c>
+      <c r="E72" s="3">
         <v>30448000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30236000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29761000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29292000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28207000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27585000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26776000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>25833000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>24766000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23846000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>22936000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21373000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19955000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19292000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18673000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19175000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>21290000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>20720000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>20107000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19484000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18906000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18354000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17787000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17211000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>16687000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>16452000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15989000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15568000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15130000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14696000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6376,8 +6552,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6471,8 +6650,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6566,103 +6748,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13664000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13772000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13180000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12800000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13259000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13288000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13230000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12708000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12377000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12352000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12207000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12115000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11098000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9828000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9196000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8587000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9102000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11296000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11154000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10930000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10696000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10567000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10453000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10326000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10308000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10329000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10627000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10699000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10705000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10763000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10787000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6756,203 +6944,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E81" s="3">
         <v>386000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>647000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>895000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>931000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1019000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>975000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1097000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1205000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1062000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1055000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1688000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1546000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>795000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>751000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-369000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-78000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>705000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>749000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>747000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>705000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>681000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>699000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>663000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>646000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>359000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>589000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>532000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>551000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>550000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6986,103 +7183,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E83" s="3">
         <v>104000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>106000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>119000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>129000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>137000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>145000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>140000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>139000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>144000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>139000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>129000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>119000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>123000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>116000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>123000</v>
       </c>
       <c r="S83" s="3">
         <v>123000</v>
       </c>
       <c r="T83" s="3">
+        <v>123000</v>
+      </c>
+      <c r="U83" s="3">
         <v>121000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>113000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>103000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>99000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>109000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>110000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>109000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>107000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>104000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>101000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>95000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>93000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>89000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7176,8 +7377,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7271,8 +7475,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7366,8 +7573,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7461,8 +7671,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7556,103 +7769,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1843000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2876000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2389000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1507000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1791000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2175000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1619000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1612000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1734000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1342000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1621000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1548000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1508000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1633000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1296000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1587000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1680000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1464000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>819000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1578000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2335000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>761000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1606000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1586000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1238000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1624000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1552000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1019000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1013000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1292000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1317000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7686,103 +7905,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-68000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-77000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-82000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-76000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-79000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-48000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-51000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-48000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-49000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-56000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-53000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-94000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-59000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-72000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-61000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-69000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-82000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-77000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-59000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-57000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-56000</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-47000</v>
       </c>
       <c r="AF91" s="3">
         <v>-47000</v>
       </c>
       <c r="AG91" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-46000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7876,8 +8099,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7971,103 +8197,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>358000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6822000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5836000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7604000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1229000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13014000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7490000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5794000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>661000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3391000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1510000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1247000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>6188000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3696000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5575000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>996000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2397000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3055000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6030000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4421000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1768000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5814000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3036000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2645000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>916000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4273000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2919000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1568000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2291000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2007000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8101,103 +8333,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-194000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-176000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-177000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-192000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-144000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-165000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-166000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-183000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-129000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-147000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-151000</v>
       </c>
       <c r="N96" s="3">
         <v>-151000</v>
       </c>
       <c r="O96" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-120000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-152000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-120000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-151000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-122000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-153000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-126000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-145000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-118000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-151000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-122000</v>
       </c>
       <c r="Z96" s="3">
         <v>-122000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-142000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-137000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-124000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-127000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-128000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-132000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8291,8 +8527,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8386,8 +8625,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8481,103 +8723,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>514000</v>
+      </c>
+      <c r="E100" s="3">
         <v>6441000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4036000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4578000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>704000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7866000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6270000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6010000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4084000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>633000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3731000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4607000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-611000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1829000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-799000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1373000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>170000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2443000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-30000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1017000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-499000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3589000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2120000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-120000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1557000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1522000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2850000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1664000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2253000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>837000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2149000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8671,99 +8919,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2715000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2495000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>589000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1519000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1266000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2973000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>399000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1828000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1689000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1416000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3620000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4306000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7085000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3500000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5078000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3956000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4247000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>852000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5241000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3860000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>68000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1464000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>690000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1179000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3711000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1483000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2213000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3249000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-162000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1459000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>DFS</t>
   </si>
@@ -656,227 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4971000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4948000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4868000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4610000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4290000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4077000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3856000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3357000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2915000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2736000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2742000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2674000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2589000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2646000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2760000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2681000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2672000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2982000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3039000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3040000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2977000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2937000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2907000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2781000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2636000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2569000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2556000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2476000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2338000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2278000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2258000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2184000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -973,8 +979,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,8 +1080,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1119,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1205,8 +1218,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1303,8 +1319,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1401,8 +1420,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1499,8 +1521,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1532,204 +1557,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2186000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2958000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3309000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2990000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2418000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2047000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1672000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1287000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>854000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>411000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>522000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>454000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>425000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>383000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>416000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>482000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>584000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1451000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1437000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1432000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1441000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1405000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1300000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1249000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1220000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1115000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1100000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1040000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>972000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>944000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2785000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1990000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1559000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1620000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1872000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2030000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2184000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2070000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2061000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2325000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>2220000</v>
       </c>
       <c r="N18" s="3">
         <v>2220000</v>
       </c>
       <c r="O18" s="3">
+        <v>2220000</v>
+      </c>
+      <c r="P18" s="3">
         <v>2164000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2695000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2377000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2265000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2190000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2398000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1588000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1603000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1545000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1496000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1502000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1481000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1387000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1349000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1441000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1376000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1298000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1306000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1314000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1380000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1764,204 +1796,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-715000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1586000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1047000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-732000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-703000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-773000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-841000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-743000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-620000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-707000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-859000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-818000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>58000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-616000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1362000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1306000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2651000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2476000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-664000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-609000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-558000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-566000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-605000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-514000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-510000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-493000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-542000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-473000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-438000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-419000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2152000</v>
+      </c>
+      <c r="E21" s="3">
         <v>500000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>616000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>994000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1288000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1386000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1480000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1472000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1581000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1757000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1505000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1541000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2351000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2198000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1138000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1075000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-338000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>45000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1045000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1107000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1090000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1029000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1006000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1077000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>986000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>963000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1004000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>962000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>961000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>972000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2058,204 +2097,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2070000</v>
+      </c>
+      <c r="E23" s="3">
         <v>404000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>512000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>888000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1169000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1257000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1343000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1327000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1441000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1618000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1361000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1402000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2222000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2079000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1015000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>959000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-461000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-78000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>924000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>994000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>987000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>930000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>897000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>967000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>877000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>856000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>899000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>903000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>867000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>868000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>883000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>961000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E24" s="3">
         <v>96000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>124000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>205000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>268000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>289000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>318000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>314000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>338000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>376000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>294000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>311000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>524000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>486000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>216000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>188000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-93000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-17000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>216000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>224000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>234000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>204000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>210000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>247000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>208000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>190000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>323000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>301000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>321000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>304000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>320000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>322000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2352,204 +2400,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1530000</v>
+      </c>
+      <c r="E26" s="3">
         <v>308000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>388000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>683000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>901000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>968000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1025000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1013000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1103000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1242000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1067000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1091000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1698000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1593000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>799000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>771000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-368000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-61000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>708000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>770000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>753000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>726000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>687000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>720000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>669000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>666000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>576000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>602000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>546000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>564000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>563000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1521000</v>
+      </c>
+      <c r="E27" s="3">
         <v>274000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>386000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>647000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>895000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>931000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1019000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>975000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1097000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1205000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1062000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1055000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1688000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1546000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>795000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>751000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-369000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-78000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>705000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>749000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>747000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>705000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>681000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>699000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>663000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>646000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>548000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>589000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>532000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>551000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>550000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2646,8 +2703,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2708,8 +2768,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2726,12 +2786,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-189000</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2744,8 +2804,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2842,8 +2905,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2940,204 +3006,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>715000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1586000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1047000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>732000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>703000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>773000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>841000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>743000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>620000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>707000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>859000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>818000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-58000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>616000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1362000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1306000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2651000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2476000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>664000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>609000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>558000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>566000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>605000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>514000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>510000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>493000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>542000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>473000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>431000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>438000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>431000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>419000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1521000</v>
+      </c>
+      <c r="E33" s="3">
         <v>274000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>386000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>647000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>895000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>931000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1019000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>975000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1097000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1205000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1062000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1055000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1688000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1546000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>795000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>751000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-369000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-78000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>705000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>749000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>747000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>705000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>681000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>699000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>663000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>646000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>359000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>589000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>532000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>551000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>550000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3234,209 +3309,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1521000</v>
+      </c>
+      <c r="E35" s="3">
         <v>274000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>386000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>647000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>895000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>931000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1019000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>975000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1097000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1205000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1062000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1055000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1688000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1546000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>795000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>751000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-369000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-78000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>705000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>749000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>747000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>705000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>681000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>699000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>663000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>646000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>359000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>589000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>532000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>551000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>550000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3471,8 +3555,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3507,106 +3592,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10865000</v>
+      </c>
+      <c r="E41" s="3">
         <v>14004000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11685000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9194000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8605000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10130000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8856000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10004000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11439000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9625000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8750000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12716000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15445000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20348000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13564000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9513000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15138000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10028000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6924000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6075000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10313000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>15169000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13299000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16019000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>15289000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>17011000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13306000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13249000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12950000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>15163000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11914000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>12076000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3650,22 +3739,22 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>2200000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>8048000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2549000</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V42" s="3">
-        <v>1000000</v>
+      <c r="V42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W42" s="3">
         <v>1000000</v>
@@ -3673,8 +3762,8 @@
       <c r="X42" s="3">
         <v>1000000</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
+      <c r="Y42" s="3">
+        <v>1000000</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>5</v>
@@ -3685,8 +3774,8 @@
       <c r="AB42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3694,17 +3783,20 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
+      <c r="AF42" s="3">
+        <v>0</v>
       </c>
       <c r="AG42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI42" s="3">
         <v>850000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3801,8 +3893,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3899,8 +3994,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3997,8 +4095,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4095,204 +4196,213 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>463000</v>
+      </c>
+      <c r="E47" s="3">
         <v>479000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>514000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>426000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>411000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>406000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>416000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>382000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>366000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>377000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>388000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>366000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>343000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>342000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>353000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>323000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>335000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>348000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>336000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>321000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>310000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>284000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>295000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>263000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>275000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>286000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>297000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>349000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>332000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>319000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>326000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>298000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1087000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1107000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1091000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1084000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1053000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1031000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1003000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1015000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>984000</v>
       </c>
       <c r="L48" s="3">
         <v>984000</v>
       </c>
       <c r="M48" s="3">
+        <v>984000</v>
+      </c>
+      <c r="N48" s="3">
         <v>983000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>987000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>986000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1021000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1027000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1121000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1115000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1070000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1106000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1028000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1008000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>980000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>936000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>896000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>874000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>848000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>825000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>800000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>774000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>750000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>734000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>722000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4327,13 +4437,13 @@
         <v>255000</v>
       </c>
       <c r="N49" s="3">
-        <v>256000</v>
+        <v>255000</v>
       </c>
       <c r="O49" s="3">
         <v>256000</v>
       </c>
       <c r="P49" s="3">
-        <v>350000</v>
+        <v>256000</v>
       </c>
       <c r="Q49" s="3">
         <v>350000</v>
@@ -4342,28 +4452,28 @@
         <v>350000</v>
       </c>
       <c r="S49" s="3">
+        <v>350000</v>
+      </c>
+      <c r="T49" s="3">
         <v>351000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>410000</v>
       </c>
       <c r="U49" s="3">
         <v>410000</v>
       </c>
       <c r="V49" s="3">
+        <v>410000</v>
+      </c>
+      <c r="W49" s="3">
         <v>414000</v>
-      </c>
-      <c r="W49" s="3">
-        <v>415000</v>
       </c>
       <c r="X49" s="3">
         <v>415000</v>
       </c>
       <c r="Y49" s="3">
+        <v>415000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>416000</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>417000</v>
       </c>
       <c r="AA49" s="3">
         <v>417000</v>
@@ -4372,25 +4482,28 @@
         <v>417000</v>
       </c>
       <c r="AC49" s="3">
-        <v>418000</v>
+        <v>417000</v>
       </c>
       <c r="AD49" s="3">
         <v>418000</v>
       </c>
       <c r="AE49" s="3">
+        <v>418000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>419000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>420000</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>421000</v>
       </c>
       <c r="AH49" s="3">
         <v>421000</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>421000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4487,8 +4600,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4585,8 +4701,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4683,8 +4802,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4781,106 +4903,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>150867000</v>
+      </c>
+      <c r="E54" s="3">
         <v>152689000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>151522000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>143432000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>138082000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>133061000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>131706000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>121886000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>114600000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>107412000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>110242000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>108544000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>110985000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>113871000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>112889000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>124349000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>113792000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>112657000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>113996000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>110786000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>110707000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>110720000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>109553000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>105842000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>102751000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>101967000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>100087000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>97608000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>93757000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>94795000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>92308000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>90541000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4915,8 +5043,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4951,8 +5080,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5049,204 +5179,213 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3725000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4476000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1312000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1316000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3290000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2331000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4122000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2638000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6935000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>5126000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4195000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4217000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11250000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1854000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4759000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5247000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>200000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2475000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3672000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6511000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1549000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2773000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3270000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5272000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1201000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2201000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4250000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5100000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1250000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7309000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7064000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6432000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5710000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4963000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4843000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5618000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4526000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4439000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4365000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4214000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4203000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3988000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3961000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3860000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3541000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3591000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3476000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3690000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3594000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4317000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4269000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3436000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4154000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3927000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3722000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4105000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3549000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3196000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3185000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3550000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3119000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5343,106 +5482,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15693000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15702000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15807000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18412000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18439000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16322000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19583000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17846000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15863000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14494000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13292000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18516000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14224000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16816000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>17024000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21291000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21340000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21339000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>20454000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>24254000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>22688000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>22604000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20717000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>25449000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>23479000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>22974000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>21054000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>25536000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>24237000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>22573000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>20343000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>25580000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5539,8 +5684,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5637,8 +5785,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5735,8 +5886,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5833,106 +5987,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>134800000</v>
+      </c>
+      <c r="E66" s="3">
         <v>137969000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>136694000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>129196000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>124226000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>118746000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>117362000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>107600000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100836000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>93979000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>96834000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>95281000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>97814000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>101717000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>102005000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>114097000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>104149000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>102992000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>102137000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>99069000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>99214000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>99461000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>98423000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>94826000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>91862000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>91096000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>89195000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>86421000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>82498000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>83530000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>80985000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>79194000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5967,8 +6127,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6065,8 +6226,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6163,8 +6327,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6217,7 +6384,7 @@
         <v>1056000</v>
       </c>
       <c r="T70" s="3">
-        <v>563000</v>
+        <v>1056000</v>
       </c>
       <c r="U70" s="3">
         <v>563000</v>
@@ -6247,7 +6414,7 @@
         <v>563000</v>
       </c>
       <c r="AD70" s="3">
-        <v>560000</v>
+        <v>563000</v>
       </c>
       <c r="AE70" s="3">
         <v>560000</v>
@@ -6261,8 +6428,11 @@
       <c r="AH70" s="3">
         <v>560000</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6359,106 +6529,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>31864000</v>
+      </c>
+      <c r="E72" s="3">
         <v>30511000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30448000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30236000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29761000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29292000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28207000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27585000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26776000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>25833000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>24766000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>23846000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>22936000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21373000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19955000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19292000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18673000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>19175000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>21290000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>20720000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>20107000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19484000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18906000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18354000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17787000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17211000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>16687000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16452000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15989000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15568000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15130000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>14696000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6555,8 +6731,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6653,8 +6832,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6751,106 +6933,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15011000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13664000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13772000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13180000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12800000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13259000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13288000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13230000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12708000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12377000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12352000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12207000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12115000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11098000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9828000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9196000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8587000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9102000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11296000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11154000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10930000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10696000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10567000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10453000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10326000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10308000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10329000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10627000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10699000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10705000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10763000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10787000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6947,209 +7135,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1521000</v>
+      </c>
+      <c r="E81" s="3">
         <v>274000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>386000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>647000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>895000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>931000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1019000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>975000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1097000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1205000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1062000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1055000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1688000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1546000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>795000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>751000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-369000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-78000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>705000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>749000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>747000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>705000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>681000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>699000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>663000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>646000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>359000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>589000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>532000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>551000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>550000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7184,106 +7381,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E83" s="3">
         <v>96000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>104000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>106000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>119000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>129000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>137000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>145000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>140000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>139000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>144000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>139000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>129000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>119000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>123000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>116000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>123000</v>
       </c>
       <c r="T83" s="3">
         <v>123000</v>
       </c>
       <c r="U83" s="3">
+        <v>123000</v>
+      </c>
+      <c r="V83" s="3">
         <v>121000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>113000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>103000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>99000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>109000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>110000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>109000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>107000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>104000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>101000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>95000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>93000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>89000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7380,8 +7581,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7478,8 +7682,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7576,8 +7783,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7674,8 +7884,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7772,106 +7985,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2578000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1843000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2876000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2389000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1507000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1791000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2175000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1619000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1612000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1734000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1342000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1621000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1548000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1508000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1633000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1296000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1587000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1680000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1464000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>819000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1578000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2335000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>761000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1606000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1586000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1238000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1624000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1552000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1019000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1013000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1292000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1317000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7906,106 +8125,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-65000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-71000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-68000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-82000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-76000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-79000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-48000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-51000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-48000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-49000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-56000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-55000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-53000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-94000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-59000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-72000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-61000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-69000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-82000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-77000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-59000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-57000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-56000</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-47000</v>
       </c>
       <c r="AG91" s="3">
         <v>-47000</v>
       </c>
       <c r="AH91" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-46000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8102,8 +8325,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8200,106 +8426,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2490000</v>
+      </c>
+      <c r="E94" s="3">
         <v>358000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6822000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5836000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7604000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1229000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13014000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7490000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5794000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>661000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3391000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1510000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1247000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>6188000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3696000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5575000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>996000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2397000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3055000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6030000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4421000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1768000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5814000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3036000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2645000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>916000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4273000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2919000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1568000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2291000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2007000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8334,106 +8566,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-193000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-194000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-176000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-177000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-192000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-144000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-165000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-166000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-183000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-129000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-147000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-151000</v>
       </c>
       <c r="O96" s="3">
         <v>-151000</v>
       </c>
       <c r="P96" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-152000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-120000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-151000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-122000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-153000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-126000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-145000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-118000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-151000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AA96" s="3">
         <v>-122000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-142000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-137000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-124000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-127000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-128000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-132000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8530,8 +8766,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8628,8 +8867,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8726,106 +8968,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3634000</v>
+      </c>
+      <c r="E100" s="3">
         <v>514000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6441000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4036000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4578000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>704000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7866000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6270000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6010000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4084000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>633000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3731000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4607000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-611000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1829000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-799000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1373000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>170000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2443000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-30000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1017000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-499000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3589000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2120000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-120000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1557000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1522000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2850000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1664000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2253000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>837000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2149000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8922,102 +9170,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3546000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2715000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2495000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>589000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1519000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1266000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2973000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>399000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1828000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1689000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1416000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3620000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4306000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7085000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3500000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5078000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3956000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4247000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>852000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5241000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3860000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>68000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1464000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>690000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1179000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3711000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1483000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2213000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3249000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-162000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1459000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>DFS</t>
   </si>
@@ -656,256 +656,262 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4971000</v>
+        <v>3759000</v>
       </c>
       <c r="E8" s="3">
-        <v>4948000</v>
+        <v>3799000</v>
       </c>
       <c r="F8" s="3">
-        <v>4868000</v>
+        <v>2713000</v>
       </c>
       <c r="G8" s="3">
-        <v>4610000</v>
+        <v>2287000</v>
       </c>
       <c r="H8" s="3">
-        <v>4290000</v>
+        <v>2342000</v>
       </c>
       <c r="I8" s="3">
-        <v>4077000</v>
+        <v>2573000</v>
       </c>
       <c r="J8" s="3">
+        <v>2640000</v>
+      </c>
+      <c r="K8" s="3">
         <v>3856000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3357000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2915000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2736000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2742000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2674000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2589000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2646000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2760000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2681000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2672000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2982000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3039000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3040000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2977000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2937000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2907000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2781000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2636000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2569000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2556000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2476000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2338000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2278000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2258000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2184000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>976000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>167000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>163000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>170000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>149000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>150000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>139000</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -982,31 +988,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>2783000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3632000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2550000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2117000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2423000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2501000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1083,8 +1092,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1120,8 +1132,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1221,8 +1234,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,31 +1338,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>131000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1423,31 +1442,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>86300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>106000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>119000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>129000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1524,8 +1546,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1558,210 +1583,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2186000</v>
+        <v>2471000</v>
       </c>
       <c r="E17" s="3">
-        <v>2958000</v>
+        <v>1729000</v>
       </c>
       <c r="F17" s="3">
-        <v>3309000</v>
+        <v>2309000</v>
       </c>
       <c r="G17" s="3">
-        <v>2990000</v>
+        <v>1644000</v>
       </c>
       <c r="H17" s="3">
-        <v>2418000</v>
+        <v>1454000</v>
       </c>
       <c r="I17" s="3">
-        <v>2047000</v>
+        <v>1404000</v>
       </c>
       <c r="J17" s="3">
+        <v>1383000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1672000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1287000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>854000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>411000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>522000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>454000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>425000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-49000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>383000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>416000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>482000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>584000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1451000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1437000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1432000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1441000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1405000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1300000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1249000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1220000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1115000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1100000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1040000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>972000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>944000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2785000</v>
+        <v>1288000</v>
       </c>
       <c r="E18" s="3">
-        <v>1990000</v>
+        <v>2070000</v>
       </c>
       <c r="F18" s="3">
-        <v>1559000</v>
+        <v>404000</v>
       </c>
       <c r="G18" s="3">
-        <v>1620000</v>
+        <v>643000</v>
       </c>
       <c r="H18" s="3">
-        <v>1872000</v>
+        <v>888000</v>
       </c>
       <c r="I18" s="3">
-        <v>2030000</v>
+        <v>1169000</v>
       </c>
       <c r="J18" s="3">
+        <v>1257000</v>
+      </c>
+      <c r="K18" s="3">
         <v>2184000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2070000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2061000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2325000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>2220000</v>
       </c>
       <c r="O18" s="3">
         <v>2220000</v>
       </c>
       <c r="P18" s="3">
+        <v>2220000</v>
+      </c>
+      <c r="Q18" s="3">
         <v>2164000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2695000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2377000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2265000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2190000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2398000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1588000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1603000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1545000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1496000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1502000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1481000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1387000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1349000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1441000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1376000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1298000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1306000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1314000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1380000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1797,233 +1829,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-715000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1586000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1047000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-732000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-703000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-773000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-841000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-743000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-620000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-707000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-859000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-818000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>58000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-616000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1362000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1306000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2651000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2476000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-664000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-609000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-558000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-566000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-605000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-514000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-510000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-493000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-542000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-473000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-438000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-419000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1370000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2152000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>500000</v>
       </c>
-      <c r="F21" s="3">
-        <v>616000</v>
-      </c>
       <c r="G21" s="3">
+        <v>729300</v>
+      </c>
+      <c r="H21" s="3">
         <v>994000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1288000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1386000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1480000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1472000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1581000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1757000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1505000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1541000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2351000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2198000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1138000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1075000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-338000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>45000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1045000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1107000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1090000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1029000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1006000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1077000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>986000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>963000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1004000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>962000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>961000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>972000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2100,210 +2139,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1288000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2070000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>404000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>512000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>888000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1169000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1257000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1343000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1327000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1441000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1618000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1361000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1402000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2222000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2079000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1015000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>959000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-461000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-78000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>924000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>994000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>987000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>930000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>897000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>967000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>877000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>856000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>899000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>903000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>867000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>868000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>883000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>961000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E24" s="3">
         <v>540000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>96000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>124000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>205000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>268000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>289000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>318000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>314000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>338000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>376000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>294000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>311000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>524000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>486000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>216000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>188000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-93000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-17000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>216000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>224000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>234000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>204000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>210000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>247000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>208000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>190000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>323000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>301000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>321000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>304000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>320000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>322000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2403,210 +2451,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>965000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1530000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>308000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>388000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>683000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>901000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>968000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1025000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1013000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1103000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1242000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1067000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1091000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1698000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1593000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>799000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>771000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-368000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-61000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>708000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>770000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>753000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>726000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>687000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>720000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>669000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>666000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>576000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>602000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>546000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>564000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>563000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>928000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1521000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>274000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>386000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>647000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>895000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>931000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1019000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>975000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1097000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1205000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1062000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1055000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1688000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1546000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>795000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>751000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-369000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-78000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>705000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>749000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>747000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>705000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>681000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>699000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>663000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>646000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>548000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>589000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>532000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>551000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>550000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2706,8 +2763,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2771,8 +2831,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2789,12 +2849,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-189000</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2807,8 +2867,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2908,8 +2971,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3009,210 +3075,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>715000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1586000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1047000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>732000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>703000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>773000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>841000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>743000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>620000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>707000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>859000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>818000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-58000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>616000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1362000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1306000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2651000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2476000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>664000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>609000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>558000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>566000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>605000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>514000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>510000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>493000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>542000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>473000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>431000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>438000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>431000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>419000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1521000</v>
+        <v>965000</v>
       </c>
       <c r="E33" s="3">
-        <v>274000</v>
+        <v>1530000</v>
       </c>
       <c r="F33" s="3">
-        <v>386000</v>
+        <v>308000</v>
       </c>
       <c r="G33" s="3">
-        <v>647000</v>
+        <v>388000</v>
       </c>
       <c r="H33" s="3">
-        <v>895000</v>
+        <v>683000</v>
       </c>
       <c r="I33" s="3">
-        <v>931000</v>
+        <v>901000</v>
       </c>
       <c r="J33" s="3">
+        <v>968000</v>
+      </c>
+      <c r="K33" s="3">
         <v>1019000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>975000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1097000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1205000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1062000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1055000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1688000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1546000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>795000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>751000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-369000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-78000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>705000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>749000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>747000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>705000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>681000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>699000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>663000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>646000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>359000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>589000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>532000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>551000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>550000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3312,215 +3387,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1521000</v>
+        <v>965000</v>
       </c>
       <c r="E35" s="3">
-        <v>274000</v>
+        <v>1530000</v>
       </c>
       <c r="F35" s="3">
-        <v>386000</v>
+        <v>308000</v>
       </c>
       <c r="G35" s="3">
-        <v>647000</v>
+        <v>388000</v>
       </c>
       <c r="H35" s="3">
-        <v>895000</v>
+        <v>683000</v>
       </c>
       <c r="I35" s="3">
-        <v>931000</v>
+        <v>901000</v>
       </c>
       <c r="J35" s="3">
+        <v>968000</v>
+      </c>
+      <c r="K35" s="3">
         <v>1019000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>975000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1097000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1205000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1062000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1055000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1688000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1546000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>795000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>751000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-369000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-78000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>705000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>749000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>747000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>705000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>681000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>699000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>663000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>646000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>359000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>589000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>532000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>551000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>550000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3556,8 +3640,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3593,109 +3678,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26423000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10865000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14004000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11685000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9194000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8605000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10130000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8856000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10004000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11439000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9625000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8750000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12716000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15445000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>20348000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13564000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9513000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15138000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10028000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6924000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6075000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10313000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>15169000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13299000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16019000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>15289000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>17011000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13306000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13249000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12950000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>15163000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>11914000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>12076000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3703,22 +3792,22 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3742,22 +3831,22 @@
         <v>0</v>
       </c>
       <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
         <v>2200000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>8048000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2549000</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W42" s="3">
-        <v>1000000</v>
+      <c r="W42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X42" s="3">
         <v>1000000</v>
@@ -3765,8 +3854,8 @@
       <c r="Y42" s="3">
         <v>1000000</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
+      <c r="Z42" s="3">
+        <v>1000000</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>5</v>
@@ -3777,8 +3866,8 @@
       <c r="AC42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3786,40 +3875,43 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
+      <c r="AG42" s="3">
+        <v>0</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>850000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>109997000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>120643000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>118787000</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>120576000</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>115407000</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>111131000</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>106247000</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3896,31 +3988,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3997,31 +4092,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4098,31 +4196,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>144904000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>131542000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>133231000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>132304000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>124654000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>119779000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>116422000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4199,210 +4300,219 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>463000</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E47" s="3">
-        <v>479000</v>
+        <v>13567000</v>
       </c>
       <c r="F47" s="3">
-        <v>514000</v>
+        <v>13659000</v>
       </c>
       <c r="G47" s="3">
-        <v>426000</v>
+        <v>13884000</v>
       </c>
       <c r="H47" s="3">
-        <v>411000</v>
+        <v>13550000</v>
       </c>
       <c r="I47" s="3">
-        <v>406000</v>
+        <v>13652000</v>
       </c>
       <c r="J47" s="3">
+        <v>12584000</v>
+      </c>
+      <c r="K47" s="3">
         <v>416000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>382000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>366000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>377000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>388000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>366000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>343000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>342000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>353000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>323000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>335000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>348000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>336000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>321000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>310000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>284000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>295000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>263000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>275000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>286000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>297000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>349000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>332000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>319000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>326000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>298000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1085000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1087000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1107000</v>
       </c>
-      <c r="F48" s="3">
-        <v>1091000</v>
-      </c>
       <c r="G48" s="3">
+        <v>388000</v>
+      </c>
+      <c r="H48" s="3">
         <v>1084000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1053000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1031000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1003000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1015000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>984000</v>
       </c>
       <c r="M48" s="3">
         <v>984000</v>
       </c>
       <c r="N48" s="3">
+        <v>984000</v>
+      </c>
+      <c r="O48" s="3">
         <v>983000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>987000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>986000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1021000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1027000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1121000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1115000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1070000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1106000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1028000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1008000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>980000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>936000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>896000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>874000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>848000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>825000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>800000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>774000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>750000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>734000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>722000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4416,7 +4526,7 @@
         <v>255000</v>
       </c>
       <c r="G49" s="3">
-        <v>255000</v>
+        <v>958000</v>
       </c>
       <c r="H49" s="3">
         <v>255000</v>
@@ -4440,13 +4550,13 @@
         <v>255000</v>
       </c>
       <c r="O49" s="3">
-        <v>256000</v>
+        <v>255000</v>
       </c>
       <c r="P49" s="3">
         <v>256000</v>
       </c>
       <c r="Q49" s="3">
-        <v>350000</v>
+        <v>256000</v>
       </c>
       <c r="R49" s="3">
         <v>350000</v>
@@ -4455,28 +4565,28 @@
         <v>350000</v>
       </c>
       <c r="T49" s="3">
+        <v>350000</v>
+      </c>
+      <c r="U49" s="3">
         <v>351000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>410000</v>
       </c>
       <c r="V49" s="3">
         <v>410000</v>
       </c>
       <c r="W49" s="3">
+        <v>410000</v>
+      </c>
+      <c r="X49" s="3">
         <v>414000</v>
-      </c>
-      <c r="X49" s="3">
-        <v>415000</v>
       </c>
       <c r="Y49" s="3">
         <v>415000</v>
       </c>
       <c r="Z49" s="3">
+        <v>415000</v>
+      </c>
+      <c r="AA49" s="3">
         <v>416000</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>417000</v>
       </c>
       <c r="AB49" s="3">
         <v>417000</v>
@@ -4485,25 +4595,28 @@
         <v>417000</v>
       </c>
       <c r="AD49" s="3">
-        <v>418000</v>
+        <v>417000</v>
       </c>
       <c r="AE49" s="3">
         <v>418000</v>
       </c>
       <c r="AF49" s="3">
+        <v>418000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>419000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>420000</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>421000</v>
       </c>
       <c r="AI49" s="3">
         <v>421000</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>421000</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4603,8 +4716,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4704,31 +4820,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>5349000</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>4416000</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>4437000</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>1305000</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>3889000</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>3343000</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>2769000</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4805,8 +4924,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4906,109 +5028,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>151593000</v>
+      </c>
+      <c r="E54" s="3">
         <v>150867000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>152689000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>151522000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>143432000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>138082000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>133061000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>131706000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>121886000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>114600000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>107412000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>110242000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>108544000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>110985000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>113871000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>112889000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>124349000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>113792000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>112657000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>113996000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>110786000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>110707000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>110720000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>109553000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>105842000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>102751000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>101967000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>100087000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>97608000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>93757000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>94795000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>92308000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>90541000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5044,8 +5172,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5081,31 +5210,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>109852000</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>108350000</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>110430000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>108931000</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>104019000</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>98987000</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>95740000</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5182,233 +5312,242 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2400000</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>3725000</v>
+        <v>2931000</v>
       </c>
       <c r="F58" s="3">
-        <v>4476000</v>
+        <v>4250000</v>
       </c>
       <c r="G58" s="3">
-        <v>7000</v>
+        <v>5001000</v>
       </c>
       <c r="H58" s="3">
-        <v>1312000</v>
+        <v>532000</v>
       </c>
       <c r="I58" s="3">
-        <v>1316000</v>
+        <v>1837000</v>
       </c>
       <c r="J58" s="3">
+        <v>1841000</v>
+      </c>
+      <c r="K58" s="3">
         <v>3290000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2331000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4122000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2638000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6935000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>5126000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4195000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4217000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11250000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1854000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4759000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5247000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>200000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2475000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3672000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6511000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1549000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2773000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3270000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5272000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1201000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2201000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4250000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5100000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1250000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>7309000</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E59" s="3">
-        <v>7064000</v>
+        <v>46000</v>
       </c>
       <c r="F59" s="3">
-        <v>6432000</v>
+        <v>34000</v>
       </c>
       <c r="G59" s="3">
-        <v>5710000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>4963000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>4843000</v>
-      </c>
-      <c r="J59" s="3">
+        <v>376000</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>5618000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4526000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4439000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4365000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4214000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4203000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3988000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3961000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3860000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3541000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3591000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3476000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3690000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3594000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4317000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4269000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3436000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4154000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3927000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3722000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4105000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3549000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3196000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3185000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3550000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3119000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>116156000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>118411000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>121561000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>120062000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>110135000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>105684000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>102327000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5485,132 +5624,138 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>15693000</v>
+        <v>18177000</v>
       </c>
       <c r="E61" s="3">
-        <v>15702000</v>
+        <v>16216000</v>
       </c>
       <c r="F61" s="3">
-        <v>15807000</v>
+        <v>16225000</v>
       </c>
       <c r="G61" s="3">
-        <v>18412000</v>
+        <v>16330000</v>
       </c>
       <c r="H61" s="3">
+        <v>18935000</v>
+      </c>
+      <c r="I61" s="3">
         <v>18439000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16322000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19583000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17846000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15863000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14494000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13292000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18516000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14224000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16816000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>17024000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21291000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21340000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>21339000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20454000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>24254000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>22688000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>22604000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20717000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>25449000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>23479000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>22974000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>21054000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>25536000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>24237000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>22573000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20343000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>25580000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>173000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>183000</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>187000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>126000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5687,8 +5832,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5788,8 +5936,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5889,8 +6040,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5990,109 +6144,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>134333000</v>
+      </c>
+      <c r="E66" s="3">
         <v>134800000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>137969000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>136694000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>129196000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>124226000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>118746000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>117362000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>107600000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100836000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>93979000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>96834000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>95281000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>97814000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>101717000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>102005000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>114097000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>104149000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>102992000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>102137000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>99069000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>99214000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>99461000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>98423000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>94826000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>91862000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>91096000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>89195000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>86421000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>82498000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>83530000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>80985000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>79194000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6128,8 +6288,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6229,8 +6390,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6330,13 +6494,16 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1056000</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>1056000</v>
@@ -6387,7 +6554,7 @@
         <v>1056000</v>
       </c>
       <c r="U70" s="3">
-        <v>563000</v>
+        <v>1056000</v>
       </c>
       <c r="V70" s="3">
         <v>563000</v>
@@ -6417,7 +6584,7 @@
         <v>563000</v>
       </c>
       <c r="AE70" s="3">
-        <v>560000</v>
+        <v>563000</v>
       </c>
       <c r="AF70" s="3">
         <v>560000</v>
@@ -6431,8 +6598,11 @@
       <c r="AI70" s="3">
         <v>560000</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>560000</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6532,109 +6702,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>31864000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30511000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30448000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>30236000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29761000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29292000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28207000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27585000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>26776000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>25833000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>24766000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>23846000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>22936000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21373000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19955000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19292000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18673000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19175000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>21290000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>20720000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>20107000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19484000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18906000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18354000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17787000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17211000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16687000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16452000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15989000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15568000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>15130000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>14696000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6734,8 +6910,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6835,8 +7014,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6936,109 +7118,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17260000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15011000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13664000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13772000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13180000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12800000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13259000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13288000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13230000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12708000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12377000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12352000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12207000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12115000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11098000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9828000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9196000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8587000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9102000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11296000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11154000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10930000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10696000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10567000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10453000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10326000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10308000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10329000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10627000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10699000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10705000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10763000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10787000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7138,215 +7326,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1521000</v>
+        <v>965000</v>
       </c>
       <c r="E81" s="3">
-        <v>274000</v>
+        <v>1530000</v>
       </c>
       <c r="F81" s="3">
-        <v>386000</v>
+        <v>308000</v>
       </c>
       <c r="G81" s="3">
-        <v>647000</v>
+        <v>388000</v>
       </c>
       <c r="H81" s="3">
-        <v>895000</v>
+        <v>683000</v>
       </c>
       <c r="I81" s="3">
-        <v>931000</v>
+        <v>901000</v>
       </c>
       <c r="J81" s="3">
+        <v>968000</v>
+      </c>
+      <c r="K81" s="3">
         <v>1019000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>975000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1097000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1205000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1062000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1055000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1688000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1546000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>795000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>751000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-369000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-78000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>705000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>749000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>747000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>705000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>681000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>699000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>663000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>646000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>359000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>589000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>532000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>551000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>550000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7382,109 +7579,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>82000</v>
+        <v>106000</v>
       </c>
       <c r="E83" s="3">
-        <v>96000</v>
+        <v>119000</v>
       </c>
       <c r="F83" s="3">
-        <v>104000</v>
+        <v>129000</v>
       </c>
       <c r="G83" s="3">
-        <v>106000</v>
+        <v>23000</v>
       </c>
       <c r="H83" s="3">
+        <v>145000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>140000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>139000</v>
+      </c>
+      <c r="K83" s="3">
+        <v>137000</v>
+      </c>
+      <c r="L83" s="3">
+        <v>145000</v>
+      </c>
+      <c r="M83" s="3">
+        <v>140000</v>
+      </c>
+      <c r="N83" s="3">
+        <v>139000</v>
+      </c>
+      <c r="O83" s="3">
+        <v>144000</v>
+      </c>
+      <c r="P83" s="3">
+        <v>139000</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>129000</v>
+      </c>
+      <c r="R83" s="3">
         <v>119000</v>
       </c>
-      <c r="I83" s="3">
-        <v>129000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>137000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>145000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>140000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>139000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>144000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>139000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>129000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>119000</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>123000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>116000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>123000</v>
       </c>
       <c r="U83" s="3">
         <v>123000</v>
       </c>
       <c r="V83" s="3">
+        <v>123000</v>
+      </c>
+      <c r="W83" s="3">
         <v>121000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>113000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>103000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>99000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>109000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>110000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>109000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>107000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>104000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>101000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>95000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>93000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>89000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7584,8 +7785,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7685,8 +7889,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7786,8 +7993,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7887,8 +8097,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7988,109 +8201,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>2578000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1843000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2876000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2389000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1507000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1791000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2175000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1619000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1612000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1734000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1342000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1621000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1508000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1633000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1296000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1587000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1680000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1464000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>819000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1578000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2335000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>761000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1606000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1586000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1238000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1624000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1552000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1019000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1013000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1292000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1317000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8126,109 +8345,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-65000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-68000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-82000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-76000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-58000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-79000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-48000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-51000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-48000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-49000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-41000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-55000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-53000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-94000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-59000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-72000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-61000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-69000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-82000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-77000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-59000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-57000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-56000</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-47000</v>
       </c>
       <c r="AH91" s="3">
         <v>-47000</v>
       </c>
       <c r="AI91" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-46000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8328,8 +8551,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8429,109 +8655,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2490000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>358000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6822000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5836000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7604000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1229000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13014000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7490000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5794000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>661000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3391000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1510000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1247000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>6188000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3696000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5575000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>996000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>2397000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3055000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6030000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4421000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1768000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5814000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3036000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2645000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>916000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4273000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2919000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1568000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2291000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2007000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8567,109 +8799,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-193000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-194000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-176000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-177000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-192000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-144000</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3">
         <v>-165000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-166000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-183000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-129000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-147000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-151000</v>
       </c>
       <c r="P96" s="3">
         <v>-151000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-120000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-152000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-120000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-151000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-122000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-153000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-126000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-145000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-118000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-151000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AB96" s="3">
         <v>-122000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-142000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-137000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-124000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-127000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-128000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-132000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8769,8 +9005,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8870,8 +9109,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8971,132 +9213,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3634000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>514000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6441000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4036000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4578000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>704000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7866000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6270000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6010000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4084000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>633000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3731000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4607000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-611000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1829000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-799000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1373000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>170000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2443000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-30000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1017000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-499000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3589000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2120000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-120000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1557000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1522000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2850000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1664000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2253000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>837000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2149000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9173,105 +9421,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3546000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2715000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2495000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>589000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1519000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1266000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2973000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>399000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1828000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1689000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1416000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3620000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4306000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7085000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3500000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5078000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3956000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4247000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>852000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5241000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3860000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>68000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1464000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>690000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1179000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3711000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1483000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2213000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3249000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-162000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1459000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DFS_QTR_FIN.xlsx
@@ -656,266 +656,272 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3759000</v>
+        <v>3557000</v>
       </c>
       <c r="E8" s="3">
+        <v>2980000</v>
+      </c>
+      <c r="F8" s="3">
         <v>3799000</v>
       </c>
-      <c r="F8" s="3">
-        <v>2713000</v>
-      </c>
       <c r="G8" s="3">
-        <v>2287000</v>
+        <v>2663000</v>
       </c>
       <c r="H8" s="3">
-        <v>2342000</v>
+        <v>2271000</v>
       </c>
       <c r="I8" s="3">
-        <v>2573000</v>
+        <v>2325000</v>
       </c>
       <c r="J8" s="3">
+        <v>2556000</v>
+      </c>
+      <c r="K8" s="3">
         <v>2640000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3856000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3357000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2915000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2736000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2742000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2674000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2589000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2646000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2760000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2681000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2672000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2982000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3039000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3040000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2977000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2937000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2907000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2781000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2636000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2569000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2556000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2476000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2338000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2278000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2258000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2184000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>976000</v>
+        <v>208000</v>
       </c>
       <c r="E9" s="3">
+        <v>197000</v>
+      </c>
+      <c r="F9" s="3">
         <v>167000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>163000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>170000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>149000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>150000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>139000</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -991,35 +997,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3349000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2783000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3632000</v>
       </c>
-      <c r="F10" s="3">
-        <v>2550000</v>
-      </c>
       <c r="G10" s="3">
-        <v>2117000</v>
+        <v>2500000</v>
       </c>
       <c r="H10" s="3">
-        <v>2193000</v>
+        <v>2101000</v>
       </c>
       <c r="I10" s="3">
-        <v>2423000</v>
+        <v>2176000</v>
       </c>
       <c r="J10" s="3">
+        <v>2406000</v>
+      </c>
+      <c r="K10" s="3">
         <v>2501000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1095,8 +1104,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1133,8 +1145,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1237,8 +1250,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,13 +1357,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>122000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1355,20 +1374,20 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>131000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1445,35 +1464,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>91000</v>
+      </c>
+      <c r="F15" s="3">
         <v>82000</v>
       </c>
-      <c r="E15" s="3">
-        <v>82000</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>96000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>86300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>106000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>119000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>129000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1549,8 +1571,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1584,216 +1609,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2471000</v>
+        <v>1733000</v>
       </c>
       <c r="E17" s="3">
-        <v>1729000</v>
+        <v>1788000</v>
       </c>
       <c r="F17" s="3">
-        <v>2309000</v>
+        <v>1738000</v>
       </c>
       <c r="G17" s="3">
-        <v>1644000</v>
+        <v>1544000</v>
       </c>
       <c r="H17" s="3">
-        <v>1454000</v>
+        <v>1657000</v>
       </c>
       <c r="I17" s="3">
+        <v>1564000</v>
+      </c>
+      <c r="J17" s="3">
         <v>1404000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1383000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1672000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1287000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>854000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>411000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>522000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>454000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>425000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-49000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>383000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>416000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>482000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>584000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1451000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1437000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1432000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1441000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1405000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1300000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1249000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1220000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1115000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1100000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1040000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>972000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>944000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1288000</v>
+        <v>1824000</v>
       </c>
       <c r="E18" s="3">
+        <v>1192000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2061000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1119000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>614000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>761000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1152000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1257000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>2184000</v>
+      </c>
+      <c r="M18" s="3">
         <v>2070000</v>
       </c>
-      <c r="F18" s="3">
-        <v>404000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>643000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>888000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1169000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1257000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>2184000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>2070000</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2061000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2325000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>2220000</v>
       </c>
       <c r="P18" s="3">
         <v>2220000</v>
       </c>
       <c r="Q18" s="3">
+        <v>2220000</v>
+      </c>
+      <c r="R18" s="3">
         <v>2164000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2695000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2377000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2265000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2190000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2398000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1588000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1603000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1545000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1496000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1502000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1481000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1387000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1349000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1441000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1376000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1298000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1306000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1314000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1380000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1830,8 +1862,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1856,190 +1889,196 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-841000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-743000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-620000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-707000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-859000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-818000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>58000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-616000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1362000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1306000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2651000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2476000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-664000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-609000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-558000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-566000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-605000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-514000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-510000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-493000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-542000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-473000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-438000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-431000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-419000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1370000</v>
+        <v>1855800</v>
       </c>
       <c r="E21" s="3">
-        <v>2152000</v>
+        <v>1283000</v>
       </c>
       <c r="F21" s="3">
-        <v>500000</v>
+        <v>2143000</v>
       </c>
       <c r="G21" s="3">
-        <v>729300</v>
+        <v>1215000</v>
       </c>
       <c r="H21" s="3">
-        <v>994000</v>
+        <v>700300</v>
       </c>
       <c r="I21" s="3">
-        <v>1288000</v>
+        <v>867000</v>
       </c>
       <c r="J21" s="3">
+        <v>1271000</v>
+      </c>
+      <c r="K21" s="3">
         <v>1386000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1480000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1472000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1581000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1757000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1505000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1541000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2351000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2198000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1138000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1075000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-338000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>45000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1045000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1107000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1090000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1029000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1006000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1077000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>986000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>963000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1004000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>962000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>961000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>972000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2064,8 +2103,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2142,216 +2181,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1288000</v>
+        <v>1702000</v>
       </c>
       <c r="E23" s="3">
-        <v>2070000</v>
+        <v>1192000</v>
       </c>
       <c r="F23" s="3">
-        <v>404000</v>
+        <v>2061000</v>
       </c>
       <c r="G23" s="3">
-        <v>512000</v>
+        <v>1119000</v>
       </c>
       <c r="H23" s="3">
-        <v>888000</v>
+        <v>483000</v>
       </c>
       <c r="I23" s="3">
-        <v>1169000</v>
+        <v>761000</v>
       </c>
       <c r="J23" s="3">
+        <v>1152000</v>
+      </c>
+      <c r="K23" s="3">
         <v>1257000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1343000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1327000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1441000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1618000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1361000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1402000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2222000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2079000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1015000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>959000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-461000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-78000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>924000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>994000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>987000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>930000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>897000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>967000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>877000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>856000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>899000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>903000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>867000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>868000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>883000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>961000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>322000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>538000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>268000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>117000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>175000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>263000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>289000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>318000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>314000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>338000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>376000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>294000</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>311000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>524000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>486000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>216000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>188000</v>
+      </c>
+      <c r="V24" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="X24" s="3">
+        <v>216000</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>224000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>234000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>204000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>210000</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>247000</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>208000</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>190000</v>
+      </c>
+      <c r="AF24" s="3">
         <v>323000</v>
       </c>
-      <c r="E24" s="3">
-        <v>540000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>96000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>124000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>205000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>268000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>289000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>318000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>314000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>338000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>376000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>294000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>311000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>524000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>486000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>216000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>188000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-93000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>216000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>224000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>234000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>204000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>210000</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>247000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>208000</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>190000</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>323000</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>301000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>321000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>304000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>320000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>322000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2454,216 +2502,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>965000</v>
+        <v>1291000</v>
       </c>
       <c r="E26" s="3">
-        <v>1530000</v>
+        <v>870000</v>
       </c>
       <c r="F26" s="3">
-        <v>308000</v>
+        <v>1523000</v>
       </c>
       <c r="G26" s="3">
-        <v>388000</v>
+        <v>851000</v>
       </c>
       <c r="H26" s="3">
-        <v>683000</v>
+        <v>366000</v>
       </c>
       <c r="I26" s="3">
-        <v>901000</v>
+        <v>586000</v>
       </c>
       <c r="J26" s="3">
+        <v>889000</v>
+      </c>
+      <c r="K26" s="3">
         <v>968000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1025000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1013000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1103000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1242000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1067000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1091000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1698000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1593000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>799000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>771000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-368000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-61000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>708000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>770000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>753000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>726000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>687000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>720000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>669000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>666000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>576000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>602000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>546000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>564000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>563000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>639000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>928000</v>
+        <v>1284000</v>
       </c>
       <c r="E27" s="3">
-        <v>1521000</v>
+        <v>834000</v>
       </c>
       <c r="F27" s="3">
-        <v>274000</v>
+        <v>1515000</v>
       </c>
       <c r="G27" s="3">
-        <v>386000</v>
+        <v>813000</v>
       </c>
       <c r="H27" s="3">
-        <v>647000</v>
+        <v>364000</v>
       </c>
       <c r="I27" s="3">
-        <v>895000</v>
+        <v>550000</v>
       </c>
       <c r="J27" s="3">
+        <v>883000</v>
+      </c>
+      <c r="K27" s="3">
         <v>931000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1019000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>975000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1097000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1205000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1062000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1055000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1688000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1546000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>795000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>751000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-369000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-78000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>705000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>749000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>747000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>705000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>681000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>699000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>663000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>646000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>548000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>589000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>532000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>551000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2766,8 +2823,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2834,8 +2894,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2852,12 +2912,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-189000</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2870,8 +2930,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2974,8 +3037,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3078,8 +3144,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3104,190 +3173,196 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>841000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>743000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>620000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>707000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>859000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>818000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-58000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>616000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1362000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1306000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2651000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2476000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>664000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>609000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>558000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>566000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>605000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>514000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>510000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>493000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>542000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>473000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>431000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>438000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>431000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>419000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>965000</v>
+        <v>1291000</v>
       </c>
       <c r="E33" s="3">
-        <v>1530000</v>
+        <v>870000</v>
       </c>
       <c r="F33" s="3">
-        <v>308000</v>
+        <v>1523000</v>
       </c>
       <c r="G33" s="3">
-        <v>388000</v>
+        <v>851000</v>
       </c>
       <c r="H33" s="3">
-        <v>683000</v>
+        <v>366000</v>
       </c>
       <c r="I33" s="3">
-        <v>901000</v>
+        <v>586000</v>
       </c>
       <c r="J33" s="3">
+        <v>889000</v>
+      </c>
+      <c r="K33" s="3">
         <v>968000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1019000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>975000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1097000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1205000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1062000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1055000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1688000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1546000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>795000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>751000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-369000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-78000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>705000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>749000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>747000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>705000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>681000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>699000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>663000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>646000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>359000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>589000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>532000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>551000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3390,221 +3465,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>965000</v>
+        <v>1291000</v>
       </c>
       <c r="E35" s="3">
-        <v>1530000</v>
+        <v>870000</v>
       </c>
       <c r="F35" s="3">
-        <v>308000</v>
+        <v>1523000</v>
       </c>
       <c r="G35" s="3">
-        <v>388000</v>
+        <v>851000</v>
       </c>
       <c r="H35" s="3">
-        <v>683000</v>
+        <v>366000</v>
       </c>
       <c r="I35" s="3">
-        <v>901000</v>
+        <v>586000</v>
       </c>
       <c r="J35" s="3">
+        <v>889000</v>
+      </c>
+      <c r="K35" s="3">
         <v>968000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1019000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>975000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1097000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1205000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1062000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1055000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1688000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1546000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>795000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>751000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-369000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-78000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>705000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>749000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>747000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>705000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>681000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>699000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>663000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>646000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>359000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>589000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>532000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>551000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3641,8 +3725,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3679,139 +3764,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>26423000</v>
+        <v>8474000</v>
       </c>
       <c r="E41" s="3">
+        <v>10787000</v>
+      </c>
+      <c r="F41" s="3">
         <v>10865000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14004000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11685000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9194000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8605000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10130000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8856000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10004000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11439000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9625000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8750000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12716000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15445000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>20348000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13564000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9513000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15138000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10028000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6924000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6075000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10313000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15169000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13299000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16019000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>15289000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>17011000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13306000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13249000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>12950000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>15163000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>11914000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>12076000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>2000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I42" s="3">
         <v>14000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3834,22 +3923,22 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
         <v>2200000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>8048000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2549000</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X42" s="3">
-        <v>1000000</v>
+      <c r="X42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y42" s="3">
         <v>1000000</v>
@@ -3857,8 +3946,8 @@
       <c r="Z42" s="3">
         <v>1000000</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
+      <c r="AA42" s="3">
+        <v>1000000</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>5</v>
@@ -3869,8 +3958,8 @@
       <c r="AD42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -3878,44 +3967,47 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>5</v>
+      <c r="AH42" s="3">
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AJ42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK42" s="3">
         <v>850000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>109997000</v>
+        <v>113793000</v>
       </c>
       <c r="E43" s="3">
+        <v>119790000</v>
+      </c>
+      <c r="F43" s="3">
         <v>120643000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>118787000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>120576000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>115407000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>111131000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>106247000</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3991,8 +4083,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4017,8 +4112,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4095,8 +4190,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4121,8 +4219,8 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4199,35 +4297,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>144904000</v>
+        <v>122293000</v>
       </c>
       <c r="E46" s="3">
+        <v>130613000</v>
+      </c>
+      <c r="F46" s="3">
         <v>131542000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>133231000</v>
       </c>
-      <c r="G46" s="3">
-        <v>132304000</v>
-      </c>
       <c r="H46" s="3">
+        <v>132308000</v>
+      </c>
+      <c r="I46" s="3">
         <v>124654000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>119779000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>116422000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4303,221 +4404,230 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
+      <c r="D47" s="3">
+        <v>20265000</v>
       </c>
       <c r="E47" s="3">
+        <v>15682000</v>
+      </c>
+      <c r="F47" s="3">
         <v>13567000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13659000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13884000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13550000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13652000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12584000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>416000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>382000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>366000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>377000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>388000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>366000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>343000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>342000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>353000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>323000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>335000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>348000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>336000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>321000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>310000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>284000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>295000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>263000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>275000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>286000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>297000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>349000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>332000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>319000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>326000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>298000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1085000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1087000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1107000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>388000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1084000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1053000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1031000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1003000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1015000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>984000</v>
       </c>
       <c r="N48" s="3">
         <v>984000</v>
       </c>
       <c r="O48" s="3">
+        <v>984000</v>
+      </c>
+      <c r="P48" s="3">
         <v>983000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>987000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>986000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1021000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1027000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1121000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1115000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1070000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1106000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1028000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1008000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>980000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>936000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>896000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>874000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>848000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>825000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>800000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>774000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>750000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>734000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>722000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>255000</v>
+        <v>968000</v>
       </c>
       <c r="E49" s="3">
         <v>255000</v>
@@ -4526,10 +4636,10 @@
         <v>255000</v>
       </c>
       <c r="G49" s="3">
+        <v>255000</v>
+      </c>
+      <c r="H49" s="3">
         <v>958000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>255000</v>
       </c>
       <c r="I49" s="3">
         <v>255000</v>
@@ -4553,13 +4663,13 @@
         <v>255000</v>
       </c>
       <c r="P49" s="3">
-        <v>256000</v>
+        <v>255000</v>
       </c>
       <c r="Q49" s="3">
         <v>256000</v>
       </c>
       <c r="R49" s="3">
-        <v>350000</v>
+        <v>256000</v>
       </c>
       <c r="S49" s="3">
         <v>350000</v>
@@ -4568,28 +4678,28 @@
         <v>350000</v>
       </c>
       <c r="U49" s="3">
+        <v>350000</v>
+      </c>
+      <c r="V49" s="3">
         <v>351000</v>
-      </c>
-      <c r="V49" s="3">
-        <v>410000</v>
       </c>
       <c r="W49" s="3">
         <v>410000</v>
       </c>
       <c r="X49" s="3">
+        <v>410000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>414000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>415000</v>
       </c>
       <c r="Z49" s="3">
         <v>415000</v>
       </c>
       <c r="AA49" s="3">
+        <v>415000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>416000</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>417000</v>
       </c>
       <c r="AC49" s="3">
         <v>417000</v>
@@ -4598,25 +4708,28 @@
         <v>417000</v>
       </c>
       <c r="AE49" s="3">
-        <v>418000</v>
+        <v>417000</v>
       </c>
       <c r="AF49" s="3">
         <v>418000</v>
       </c>
       <c r="AG49" s="3">
+        <v>418000</v>
+      </c>
+      <c r="AH49" s="3">
         <v>419000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>420000</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>421000</v>
       </c>
       <c r="AJ49" s="3">
         <v>421000</v>
       </c>
+      <c r="AK49" s="3">
+        <v>421000</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4719,8 +4832,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4823,35 +4939,38 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5349000</v>
+        <v>1035000</v>
       </c>
       <c r="E52" s="3">
+        <v>3980000</v>
+      </c>
+      <c r="F52" s="3">
         <v>4416000</v>
       </c>
-      <c r="F52" s="3">
-        <v>4437000</v>
-      </c>
       <c r="G52" s="3">
-        <v>1305000</v>
+        <v>4455000</v>
       </c>
       <c r="H52" s="3">
+        <v>1301000</v>
+      </c>
+      <c r="I52" s="3">
         <v>3889000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3343000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2769000</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4927,8 +5046,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5031,112 +5153,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>151593000</v>
+        <v>147640000</v>
       </c>
       <c r="E54" s="3">
+        <v>151615000</v>
+      </c>
+      <c r="F54" s="3">
         <v>150867000</v>
       </c>
-      <c r="F54" s="3">
-        <v>152689000</v>
-      </c>
       <c r="G54" s="3">
-        <v>151522000</v>
+        <v>152707000</v>
       </c>
       <c r="H54" s="3">
+        <v>151713000</v>
+      </c>
+      <c r="I54" s="3">
         <v>143432000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>138082000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>133061000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>131706000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>121886000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>114600000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>107412000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>110242000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>108544000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>110985000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>113871000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>112889000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>124349000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>113792000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>112657000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>113996000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>110786000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>110707000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>110720000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>109553000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>105842000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>102751000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>101967000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>100087000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>97608000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>93757000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>94795000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>92308000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>90541000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5173,8 +5301,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5211,35 +5340,36 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>107009000</v>
+      </c>
+      <c r="E57" s="3">
         <v>109852000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>108350000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>110430000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>108931000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>104019000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>98987000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>95740000</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -5315,129 +5445,135 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>6171000</v>
       </c>
       <c r="E58" s="3">
-        <v>2931000</v>
+        <v>1812000</v>
       </c>
       <c r="F58" s="3">
+        <v>2936000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>4261000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>750000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>532000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1837000</v>
+      </c>
+      <c r="K58" s="3">
+        <v>1841000</v>
+      </c>
+      <c r="L58" s="3">
+        <v>3290000</v>
+      </c>
+      <c r="M58" s="3">
+        <v>2331000</v>
+      </c>
+      <c r="N58" s="3">
+        <v>4122000</v>
+      </c>
+      <c r="O58" s="3">
+        <v>2638000</v>
+      </c>
+      <c r="P58" s="3">
+        <v>6935000</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>5126000</v>
+      </c>
+      <c r="S58" s="3">
+        <v>4195000</v>
+      </c>
+      <c r="T58" s="3">
+        <v>4217000</v>
+      </c>
+      <c r="U58" s="3">
+        <v>11250000</v>
+      </c>
+      <c r="V58" s="3">
+        <v>1854000</v>
+      </c>
+      <c r="W58" s="3">
+        <v>4759000</v>
+      </c>
+      <c r="X58" s="3">
+        <v>5247000</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>200000</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>2475000</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>3672000</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>6511000</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>1549000</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>2773000</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>3270000</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>5272000</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>2201000</v>
+      </c>
+      <c r="AI58" s="3">
         <v>4250000</v>
       </c>
-      <c r="G58" s="3">
-        <v>5001000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>532000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1837000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1841000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>3290000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2331000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>4122000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>2638000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>6935000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>5126000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>4195000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>4217000</v>
-      </c>
-      <c r="T58" s="3">
-        <v>11250000</v>
-      </c>
-      <c r="U58" s="3">
-        <v>1854000</v>
-      </c>
-      <c r="V58" s="3">
-        <v>4759000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>5247000</v>
-      </c>
-      <c r="X58" s="3">
-        <v>200000</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>2475000</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>3672000</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>6511000</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>1549000</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>2773000</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>3270000</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>5272000</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>1201000</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>2201000</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>4250000</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>5100000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1250000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="3">
+        <v>1240000</v>
       </c>
       <c r="E59" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F59" s="3">
         <v>46000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>34000</v>
       </c>
-      <c r="G59" s="3">
-        <v>376000</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
+      <c r="H59" s="3">
+        <v>1000</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
@@ -5445,113 +5581,116 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>5618000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4526000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4439000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4365000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4214000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4203000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3988000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3961000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3860000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3541000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3591000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3476000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3690000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3594000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4317000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4269000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3436000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4154000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3927000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3722000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4105000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3549000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3196000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3185000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3550000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3119000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>116156000</v>
+        <v>119408000</v>
       </c>
       <c r="E60" s="3">
+        <v>117948000</v>
+      </c>
+      <c r="F60" s="3">
         <v>118411000</v>
       </c>
-      <c r="F60" s="3">
-        <v>121561000</v>
-      </c>
       <c r="G60" s="3">
-        <v>120062000</v>
+        <v>121629000</v>
       </c>
       <c r="H60" s="3">
+        <v>116710000</v>
+      </c>
+      <c r="I60" s="3">
         <v>110135000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>105684000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>102327000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5627,139 +5766,145 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18177000</v>
+        <v>10083000</v>
       </c>
       <c r="E61" s="3">
+        <v>16402000</v>
+      </c>
+      <c r="F61" s="3">
         <v>16216000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16225000</v>
       </c>
-      <c r="G61" s="3">
-        <v>16330000</v>
-      </c>
       <c r="H61" s="3">
+        <v>20581000</v>
+      </c>
+      <c r="I61" s="3">
         <v>18935000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18439000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16322000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19583000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17846000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15863000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14494000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13292000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18516000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14224000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16816000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17024000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21291000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>21340000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>21339000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20454000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>24254000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>22688000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>22604000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20717000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>25449000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>23479000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>22974000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>21054000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>25536000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>24237000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>22573000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>20343000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>25580000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3">
+        <v>223000</v>
       </c>
       <c r="E62" s="3">
+        <v>156000</v>
+      </c>
+      <c r="F62" s="3">
         <v>173000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>183000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>187000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>126000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>103000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>97000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5835,8 +5980,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5939,8 +6087,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6043,8 +6194,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6147,112 +6301,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>134333000</v>
+        <v>129714000</v>
       </c>
       <c r="E66" s="3">
+        <v>134506000</v>
+      </c>
+      <c r="F66" s="3">
         <v>134800000</v>
       </c>
-      <c r="F66" s="3">
-        <v>137969000</v>
-      </c>
       <c r="G66" s="3">
-        <v>136694000</v>
+        <v>138037000</v>
       </c>
       <c r="H66" s="3">
+        <v>137478000</v>
+      </c>
+      <c r="I66" s="3">
         <v>129196000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>124226000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>118746000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>117362000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>107600000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>100836000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>93979000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>96834000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>95281000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>97814000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>101717000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>102005000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>114097000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>104149000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>102992000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>102137000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>99069000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>99214000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>99461000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>98423000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>94826000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>91862000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>91096000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>89195000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>86421000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>82498000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>83530000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>80985000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>79194000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6289,8 +6449,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6393,8 +6554,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6497,13 +6661,16 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>1056000</v>
       </c>
       <c r="E70" s="3">
         <v>1056000</v>
@@ -6557,7 +6724,7 @@
         <v>1056000</v>
       </c>
       <c r="V70" s="3">
-        <v>563000</v>
+        <v>1056000</v>
       </c>
       <c r="W70" s="3">
         <v>563000</v>
@@ -6587,7 +6754,7 @@
         <v>563000</v>
       </c>
       <c r="AF70" s="3">
-        <v>560000</v>
+        <v>563000</v>
       </c>
       <c r="AG70" s="3">
         <v>560000</v>
@@ -6601,8 +6768,11 @@
       <c r="AJ70" s="3">
         <v>560000</v>
       </c>
+      <c r="AK70" s="3">
+        <v>560000</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6705,112 +6875,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>33583000</v>
       </c>
       <c r="E72" s="3">
+        <v>32469000</v>
+      </c>
+      <c r="F72" s="3">
         <v>31864000</v>
       </c>
-      <c r="F72" s="3">
-        <v>30511000</v>
-      </c>
       <c r="G72" s="3">
-        <v>30448000</v>
+        <v>30461000</v>
       </c>
       <c r="H72" s="3">
+        <v>29855000</v>
+      </c>
+      <c r="I72" s="3">
         <v>30236000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29761000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29292000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28207000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27585000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>26776000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>25833000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>24766000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>23846000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>22936000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>21373000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19955000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>19292000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18673000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19175000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>21290000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>20720000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>20107000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19484000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18906000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18354000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17787000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17211000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16687000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16452000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15989000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>15568000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>15130000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>14696000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6913,8 +7089,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7017,8 +7196,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7121,112 +7303,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>17260000</v>
+        <v>16870000</v>
       </c>
       <c r="E76" s="3">
+        <v>16053000</v>
+      </c>
+      <c r="F76" s="3">
         <v>15011000</v>
       </c>
-      <c r="F76" s="3">
-        <v>13664000</v>
-      </c>
       <c r="G76" s="3">
-        <v>13772000</v>
+        <v>13614000</v>
       </c>
       <c r="H76" s="3">
+        <v>13179000</v>
+      </c>
+      <c r="I76" s="3">
         <v>13180000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12800000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13259000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13288000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13230000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12708000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12377000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12352000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12207000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12115000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11098000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9828000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9196000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8587000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9102000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11296000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11154000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10930000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10696000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10567000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10453000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10326000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10308000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10329000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10627000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10699000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10705000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10763000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10787000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7329,221 +7517,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>965000</v>
+        <v>1291000</v>
       </c>
       <c r="E81" s="3">
-        <v>1530000</v>
+        <v>870000</v>
       </c>
       <c r="F81" s="3">
-        <v>308000</v>
+        <v>1523000</v>
       </c>
       <c r="G81" s="3">
-        <v>388000</v>
+        <v>851000</v>
       </c>
       <c r="H81" s="3">
-        <v>683000</v>
+        <v>366000</v>
       </c>
       <c r="I81" s="3">
-        <v>901000</v>
+        <v>586000</v>
       </c>
       <c r="J81" s="3">
+        <v>889000</v>
+      </c>
+      <c r="K81" s="3">
         <v>968000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1019000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>975000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1097000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1205000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1062000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1055000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1688000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1546000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>795000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>751000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-369000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-78000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>705000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>749000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>747000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>705000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>681000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>699000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>663000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>646000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>359000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>589000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>532000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>551000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>625000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7580,112 +7777,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E83" s="3">
         <v>106000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>119000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>129000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>145000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>140000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>139000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>137000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>145000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>140000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>139000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>144000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>139000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>129000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>119000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>123000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>116000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>123000</v>
       </c>
       <c r="V83" s="3">
         <v>123000</v>
       </c>
       <c r="W83" s="3">
+        <v>123000</v>
+      </c>
+      <c r="X83" s="3">
         <v>121000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>113000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>103000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>99000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>109000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>110000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>109000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>107000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>104000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>101000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>95000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>93000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>89000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7788,8 +7989,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7892,8 +8096,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7996,8 +8203,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8100,8 +8310,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8204,112 +8417,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>1980000</v>
       </c>
       <c r="E89" s="3">
+        <v>2024000</v>
+      </c>
+      <c r="F89" s="3">
         <v>2578000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1843000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2876000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2389000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1507000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1791000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2175000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1619000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1612000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1734000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1342000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1621000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1548000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1508000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1633000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1296000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1587000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1680000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1464000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>819000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1578000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2335000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>761000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1606000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1586000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1238000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1624000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1552000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1019000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1013000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1292000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1317000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8346,112 +8565,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-63000</v>
       </c>
       <c r="E91" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-65000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-71000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-68000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-77000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-82000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-76000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-58000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-79000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-48000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-51000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-48000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-56000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-41000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-55000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-53000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-94000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-59000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-72000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-69000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-77000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-59000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-57000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-56000</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-47000</v>
       </c>
       <c r="AI91" s="3">
         <v>-47000</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-46000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8554,8 +8777,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8658,112 +8884,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>619000</v>
       </c>
       <c r="E94" s="3">
+        <v>-2238000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2490000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>358000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6822000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5836000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7604000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1229000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13014000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7490000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5794000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>661000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3391000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1510000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1247000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>6188000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>3696000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5575000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>996000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2397000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3055000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6030000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4421000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5814000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3036000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2645000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>916000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4273000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2919000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1568000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2291000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2007000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8800,8 +9032,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8826,86 +9059,89 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
         <v>-165000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-166000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-183000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-129000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-147000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-151000</v>
       </c>
       <c r="Q96" s="3">
         <v>-151000</v>
       </c>
       <c r="R96" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-120000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-152000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-120000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-151000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-122000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-153000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-126000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-145000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-118000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-151000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AC96" s="3">
         <v>-122000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-142000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-137000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-124000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-127000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-128000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-132000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9008,8 +9244,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9112,8 +9351,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9216,112 +9458,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>-4923000</v>
       </c>
       <c r="E100" s="3">
+        <v>140000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3634000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>514000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6441000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4036000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4578000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>704000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7866000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6270000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6010000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4084000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>633000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3731000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4607000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-611000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1829000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-799000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1373000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>170000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2443000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-30000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1017000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-499000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3589000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2120000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-120000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1557000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1522000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2850000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1664000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2253000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>837000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2149000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9346,8 +9594,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9424,108 +9672,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-2324000</v>
       </c>
       <c r="E102" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3546000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2715000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2495000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>589000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1519000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1266000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2973000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>399000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1828000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1689000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1416000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3620000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4306000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7085000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3500000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5078000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3956000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4247000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>852000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5241000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3860000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>68000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1464000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>690000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1179000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3711000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1483000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2213000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3249000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-162000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1459000</v>
       </c>
     </row>
